--- a/Luban/Config/Datas/Levels/L16/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L16/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L16 W1/25; N=46; EHP=283.360000; normal:17x23,normal:18x23</t>
+          <t>L16 W1/25; N=46; EHP=693.174018; normal:17x23,normal:18x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L16 W2/25; N=52; EHP=335.407072; normal:17x26,normal:18x26</t>
+          <t>L16 W2/25; N=52; EHP=820.495016; normal:17x26,normal:18x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>3704136,3704673,3704019,3704136,3704673,3704019,3704136,3704673,3704091,3704136,3704673,3704099,3704136,3704673,3704099,3704136,3704673,3704107,3704136,3704673,3704115,3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704136,3704144,3704144,3704144,3704144,3704144,3704144,3704144,3704144,3704144,3704144,3704144,3704144,3704144,3704144,3704144,3704144,3704144</t>
+          <t>3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704673,3704136,3704136,3704144,3704144,3704144,3704144,3704144,3704144,3704144,3704144,3704144,3704144,3704144,3704144,3704144,3704144,3704144,3704144,3704144,3704136,3704136,3704136,3704136,3704136,3704136,3704136</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L16 W3/25; N=58; EHP=413.873152; air:2x2,air:11x1,air:12x2,air:13x1,air:14x1,normal:17x18,normal:18x17,swarm:84x16</t>
+          <t>L16 W3/25; N=58; EHP=1092.730435; normal:17x25,normal:18x17,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>3706136,3706673,3706019,3706136,3706673,3706019,3706136,3706673,3706091,3706136,3706673,3706091,3706136,3706673,3706099,3706136,3706673,3706107,3706136,3706673,3706107,3706136,3706673,3706115,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706136,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144</t>
+          <t>3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706673,3706136,3706136,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144,3706144</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L16 W4/25; N=64; EHP=525.876736; air:2x2,air:11x2,air:12x1,air:13x2,air:14x1,normal:17x19,normal:18x20,swarm:84x17</t>
+          <t>L16 W4/25; N=64; EHP=1391.938952; normal:17x19,normal:18x28,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>3708136,3708673,3708019,3708668,3708136,3708673,3708091,3708668,3708136,3708673,3708091,3708668,3708136,3708673,3708099,3708668,3708136,3708673,3708107,3708868,3708136,3708673,3708107,3708868,3708136,3708673,3708115,3708868,3708136,3708673,3708115,3708988,3708136,3708673,3708988,3708136,3708673,3708988,3708136,3708673,3708136,3708673,3708136,3708673,3708136,3708673,3708136,3708673,3708136,3708673,3708136,3708673,3708144,3708673,3708144,3708673,3708144,3708144,3708144,3708144,3708144,3708144,3708144,3708144,3708144,3708144,3708144,3708144,3708144,3708144</t>
+          <t>3708136,3708019,3708019,3708668,3708136,3708091,3708091,3708668,3708136,3708091,3708091,3708668,3708136,3708099,3708099,3708668,3708136,3708107,3708107,3708868,3708136,3708107,3708107,3708868,3708136,3708115,3708115,3708868,3708136,3708115,3708115,3708988,3708136,3708673,3708988,3708136,3708673,3708988,3708136,3708673,3708136,3708673,3708136,3708673,3708136,3708673,3708136,3708673,3708136,3708673,3708136,3708673,3708144,3708673,3708144,3708673,3708144,3708144,3708144,3708144,3708144,3708144,3708144,3708144,3708144,3708144,3708144,3708144,3708144,3708144</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L16 W5/25; N=70; EHP=990.663027; air:2x1,air:11x2,air:12x1,air:13x2,air:14x2,normal:17x17,normal:18x16,medium:83x4,swarm:84x19,medium:108x3,medium:123x3</t>
+          <t>L16 W5/25; N=70; EHP=2452.822700; air:2x2,air:11x4,air:12x2,air:13x4,air:14x4,medium:83x4,medium:108x3,medium:123x3,normal:17x17,normal:18x16,swarm:84x11 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>3710136,3710673,3710242,3710019,3710668,3710136,3710673,3710242,3710019,3710668,3710136,3710673,3710466,3710091,3710668,3710136,3710673,3710466,3710091,3710868,3710136,3710673,3710466,3710099,3710868,3710136,3710673,3710514,3710099,3710868,3710136,3710673,3710514,3710107,3710868,3710136,3710673,3710786,3710115,3710988,3710136,3710673,3710786,3710115,3710988,3710136,3710673,3710988,3710136,3710673,3710988,3710136,3710673,3710136,3710673,3710144,3710673,3710144,3710673,3710144,3710673,3710144,3710673,3710144,3710673,3710144,3710673,3710144,3710673,3710144,3710673,3710144,3710144,3710144,3710144,3710144</t>
+          <t>3710136,3710019,3710242,3710019,3710668,3710136,3710019,3710242,3710019,3710668,3710136,3710091,3710466,3710091,3710668,3710136,3710091,3710466,3710091,3710868,3710136,3710099,3710466,3710099,3710868,3710136,3710099,3710514,3710099,3710868,3710136,3710107,3710514,3710107,3710868,3710136,3710115,3710786,3710115,3710988,3710136,3710115,3710786,3710115,3710988,3710136,3710673,3710988,3710136,3710673,3710988,3710136,3710673,3710136,3710673,3710144,3710673,3710144,3710673,3710144,3710673,3710144,3710673,3710144,3710673,3710144,3710673,3710144,3710673,3710144,3710673,3710144,3710144,3710144,3710144,3710144</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L16 W6/25; N=76; EHP=1011.000000; air:2x2,air:11x2,air:12x2,air:13x1,air:14x2,normal:17x13,normal:18x13,fast:30x2,fast:58x3,fast:64x2,medium:83x3,swarm:84x21,fast:98x2,medium:108x4,medium:123x4</t>
+          <t>L16 W6/25; N=76; EHP=2504.950496; air:2x4,air:11x4,air:12x4,air:13x2,air:14x4,fast:30x2,fast:58x3,fast:64x2,fast:98x2,medium:83x3,medium:108x4,medium:123x4,normal:17x13,normal:18x13,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>3712136,3712673,3712242,3712019,3712668,3712136,3712673,3712242,3712019,3712668,3712136,3712673,3712466,3712091,3712668,3712136,3712673,3712466,3712091,3712668,3712136,3712673,3712514,3712099,3712868,3712136,3712673,3712514,3712099,3712868,3712136,3712673,3712514,3712107,3712868,3712136,3712673,3712786,3712107,3712868,3712136,3712673,3712786,3712115,3712988,3712136,3712673,3712115,3712988,3712136,3712673,3712988,3712136,3712673,3712988,3712136,3712673,3712136,3712673,3712136,3712673,3712144,3712673,3712144,3712673,3712144,3712673,3712144,3712673,3712144,3712673,3712144,3712673,3712144,3712673,3712144,3712144,3712144,3712144,3712144,3712144,3712144</t>
+          <t>3712136,3712019,3712242,3712019,3712668,3712136,3712019,3712242,3712019,3712668,3712136,3712091,3712466,3712091,3712668,3712136,3712091,3712466,3712091,3712668,3712136,3712099,3712514,3712099,3712868,3712136,3712099,3712514,3712099,3712868,3712136,3712107,3712514,3712107,3712868,3712136,3712107,3712786,3712107,3712868,3712136,3712115,3712786,3712115,3712988,3712136,3712115,3712115,3712988,3712136,3712673,3712988,3712136,3712673,3712988,3712136,3712673,3712136,3712673,3712136,3712673,3712144,3712673,3712144,3712673,3712144,3712673,3712144,3712673,3712144,3712673,3712144,3712673,3712144,3712673,3712144,3712144,3712144,3712144,3712144,3712144,3712144</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L16 W7/25; N=82; EHP=1137.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x15,normal:18x14,fast:30x2,fast:58x2,fast:64x3,medium:83x4,swarm:84x22,fast:98x2,medium:108x4,medium:123x4</t>
+          <t>L16 W7/25; N=82; EHP=2818.074585; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x2,fast:58x2,fast:64x3,fast:98x2,medium:83x4,medium:108x4,medium:123x4,normal:17x15,normal:18x14,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>3714136,3714673,3714242,3714019,3714668,3714136,3714673,3714242,3714019,3714668,3714136,3714673,3714242,3714091,3714668,3714136,3714673,3714466,3714091,3714668,3714136,3714673,3714466,3714099,3714668,3714136,3714673,3714514,3714099,3714868,3714136,3714673,3714514,3714099,3714868,3714136,3714673,3714786,3714107,3714868,3714136,3714673,3714786,3714107,3714868,3714136,3714673,3714786,3714115,3714988,3714136,3714673,3714115,3714988,3714136,3714673,3714988,3714136,3714673,3714988,3714136,3714673,3714136,3714673,3714144,3714673,3714144,3714673,3714144,3714673,3714144,3714673,3714144,3714673,3714144,3714673,3714144,3714673,3714144,3714673,3714144,3714673,3714144,3714144,3714144,3714144,3714144,3714144</t>
+          <t>3714136,3714019,3714242,3714019,3714668,3714136,3714019,3714242,3714019,3714668,3714136,3714091,3714242,3714091,3714668,3714136,3714091,3714466,3714091,3714668,3714136,3714099,3714466,3714099,3714668,3714136,3714099,3714514,3714099,3714868,3714136,3714099,3714514,3714099,3714868,3714136,3714107,3714786,3714107,3714868,3714136,3714107,3714786,3714107,3714868,3714136,3714115,3714786,3714115,3714988,3714136,3714115,3714115,3714988,3714136,3714673,3714988,3714136,3714673,3714988,3714136,3714673,3714136,3714673,3714144,3714673,3714144,3714673,3714144,3714673,3714144,3714673,3714144,3714673,3714144,3714673,3714144,3714673,3714144,3714673,3714144,3714673,3714144,3714144,3714144,3714144,3714144,3714144</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L16 W8/25; N=88; EHP=1462.000000; air:2x2,air:11x2,air:12x3,air:13x2,air:14x2,normal:17x15,normal:18x15,fast:30x3,fast:58x2,fast:64x2,medium:83x5,swarm:84x24,fast:98x3,medium:108x4,medium:123x4</t>
+          <t>L16 W8/25; N=88; EHP=3624.920505; air:2x4,air:11x4,air:12x6,air:13x4,air:14x4,fast:30x3,fast:58x2,fast:64x2,fast:98x3,medium:83x5,medium:108x4,medium:123x4,normal:17x15,normal:18x15,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>3716136,3716673,3716242,3716019,3716668,3716136,3716673,3716242,3716019,3716668,3716136,3716673,3716466,3716019,3716668,3716136,3716673,3716466,3716091,3716668,3716136,3716673,3716466,3716091,3716868,3716136,3716673,3716514,3716099,3716868,3716136,3716673,3716514,3716099,3716868,3716136,3716673,3716514,3716107,3716868,3716136,3716673,3716786,3716107,3716868,3716136,3716673,3716786,3716115,3716988,3716136,3716673,3716786,3716115,3716988,3716136,3716673,3716988,3716136,3716673,3716988,3716136,3716673,3716988,3716136,3716673,3716136,3716673,3716144,3716673,3716144,3716673,3716144,3716673,3716144,3716673,3716144,3716673,3716144,3716673,3716144,3716673,3716144,3716673,3716144,3716673,3716144,3716673,3716144,3716144,3716144,3716144,3716144,3716144</t>
+          <t>3716136,3716019,3716242,3716019,3716668,3716136,3716019,3716242,3716019,3716668,3716136,3716019,3716466,3716019,3716668,3716136,3716091,3716466,3716091,3716668,3716136,3716091,3716466,3716091,3716868,3716136,3716099,3716514,3716099,3716868,3716136,3716099,3716514,3716099,3716868,3716136,3716107,3716514,3716107,3716868,3716136,3716107,3716786,3716107,3716868,3716136,3716115,3716786,3716115,3716988,3716136,3716115,3716786,3716115,3716988,3716136,3716673,3716988,3716136,3716673,3716988,3716136,3716673,3716988,3716136,3716673,3716136,3716673,3716144,3716673,3716144,3716673,3716144,3716673,3716144,3716673,3716144,3716673,3716144,3716673,3716144,3716673,3716144,3716673,3716144,3716673,3716144,3716673,3716144,3716144,3716144,3716144,3716144,3716144</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L16 W9/25; N=94; EHP=1866.000000; air:2x3,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x16,normal:18x16,fast:30x2,fast:58x3,fast:64x3,medium:83x4,swarm:84x26,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L16 W9/25; N=94; EHP=4622.447923; air:2x6,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x2,fast:58x3,fast:64x3,fast:98x3,medium:83x4,medium:108x5,medium:123x5,normal:17x16,normal:18x16,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>3718136,3718673,3718242,3718019,3718668,3718136,3718673,3718242,3718019,3718668,3718136,3718673,3718242,3718091,3718668,3718136,3718673,3718466,3718091,3718668,3718136,3718673,3718466,3718091,3718668,3718136,3718673,3718466,3718099,3718868,3718136,3718673,3718514,3718099,3718868,3718136,3718673,3718514,3718107,3718868,3718136,3718673,3718514,3718107,3718868,3718136,3718673,3718786,3718107,3718868,3718136,3718673,3718786,3718115,3718988,3718136,3718673,3718786,3718115,3718988,3718136,3718673,3718988,3718136,3718673,3718988,3718136,3718673,3718988,3718136,3718673,3718144,3718673,3718144,3718673,3718144,3718673,3718144,3718673,3718144,3718673,3718144,3718673,3718144,3718673,3718144,3718673,3718144,3718673,3718144,3718673,3718144,3718673,3718144,3718673,3718144,3718144,3718144,3718144,3718144</t>
+          <t>3718136,3718019,3718242,3718019,3718668,3718136,3718019,3718242,3718019,3718668,3718136,3718091,3718242,3718091,3718668,3718136,3718091,3718466,3718091,3718668,3718136,3718091,3718466,3718091,3718668,3718136,3718099,3718466,3718099,3718868,3718136,3718099,3718514,3718099,3718868,3718136,3718107,3718514,3718107,3718868,3718136,3718107,3718514,3718107,3718868,3718136,3718107,3718786,3718107,3718868,3718136,3718115,3718786,3718115,3718988,3718136,3718115,3718786,3718115,3718988,3718136,3718673,3718988,3718136,3718673,3718988,3718136,3718673,3718988,3718136,3718673,3718144,3718673,3718144,3718673,3718144,3718673,3718144,3718673,3718144,3718673,3718144,3718673,3718144,3718673,3718144,3718673,3718144,3718673,3718144,3718673,3718144,3718673,3718144,3718673,3718144,3718144,3718144,3718144,3718144</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L16 W10/25; N=100; EHP=3442.000000; air:2x2,air:11x3,air:12x2,air:13x3,air:14x2,normal:17x16,normal:18x17,fast:30x3,fast:58x3,fast:64x3,medium:83x5,swarm:84x28,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L16 W10/25; N=100; EHP=8529.518346; air:2x4,air:11x6,air:12x4,air:13x6,air:14x4,fast:30x3,fast:58x3,fast:64x3,fast:98x3,medium:83x5,medium:108x5,medium:123x5,normal:17x16,normal:18x17,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>3720136,3720673,3720242,3720019,3720668,3720253,3720136,3720673,3720242,3720019,3720668,3720253,3720136,3720673,3720242,3720091,3720668,3720325,3720136,3720673,3720466,3720091,3720668,3720325,3720136,3720673,3720466,3720091,3720668,3720541,3720136,3720673,3720466,3720099,3720868,3720565,3720136,3720673,3720514,3720099,3720868,3720645,3720136,3720673,3720514,3720099,3720868,3720693,3720136,3720673,3720514,3720107,3720868,3720709,3720136,3720673,3720786,3720107,3720868,3721021,3720136,3720673,3720786,3720115,3720988,3720136,3720673,3720786,3720115,3720988,3720136,3720673,3720115,3720988,3720136,3720673,3720988,3720144,3720673,3720988,3720144,3720673,3720144,3720673,3720144,3720673,3720144,3720673,3720144,3720673,3720144,3720673,3720144,3720673,3720144,3720673,3720144,3720673,3720144,3720673,3720144,3720673,3720144,3720673,3720673,3720673</t>
+          <t>3720136,3720019,3720242,3720019,3720668,3720253,3720136,3720019,3720242,3720019,3720668,3720253,3720136,3720091,3720242,3720091,3720668,3720325,3720136,3720091,3720466,3720091,3720668,3720325,3720136,3720091,3720466,3720091,3720668,3720541,3720136,3720099,3720466,3720099,3720868,3720565,3720136,3720099,3720514,3720099,3720868,3720645,3720136,3720099,3720514,3720099,3720868,3720693,3720136,3720107,3720514,3720107,3720868,3720709,3720136,3720107,3720786,3720107,3720868,3721021,3720136,3720115,3720786,3720115,3720988,3720136,3720115,3720786,3720115,3720988,3720136,3720115,3720115,3720988,3720136,3720673,3720988,3720144,3720673,3720988,3720144,3720673,3720144,3720673,3720144,3720673,3720144,3720673,3720144,3720673,3720144,3720673,3720144,3720673,3720144,3720673,3720144,3720673,3720144,3720673,3720144,3720673,3720144,3720673,3720673,3720673</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L16 W11/25; N=106; EHP=3511.000000; air:2x2,air:11x3,air:12x3,air:13x2,air:14x3,normal:17x14,normal:18x13,fast:30x3,heavy:31x2,heavy:40x2,fast:58x3,fast:64x3,heavy:67x1,heavy:70x1,heavy:80x1,medium:83x5,swarm:84x29,heavy:86x1,heavy:88x1,fast:98x3,medium:108x5,medium:123x5,heavy:127x1</t>
+          <t>L16 W11/25; N=106; EHP=8690.902148; air:2x4,air:11x6,air:12x6,air:13x4,air:14x6,fast:30x3,fast:58x3,fast:64x3,fast:98x3,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x1,medium:83x5,medium:108x5,medium:123x5,normal:17x14,normal:18x13,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>3722136,3722673,3722242,3722019,3722668,3722253,3722136,3722673,3722242,3722019,3722668,3722325,3722136,3722673,3722242,3722019,3722668,3722325,3722136,3722673,3722242,3722091,3722668,3722541,3722136,3722673,3722466,3722091,3722668,3722565,3722136,3722673,3722466,3722099,3722868,3722565,3722136,3722673,3722466,3722099,3722868,3722645,3722136,3722673,3722514,3722099,3722868,3722693,3722136,3722673,3722514,3722107,3722868,3722709,3722136,3722673,3722514,3722107,3722868,3723021,3722136,3722673,3722786,3722115,3722988,3723021,3722136,3722673,3722786,3722115,3722988,3722136,3722673,3722786,3722115,3722988,3722136,3722673,3722988,3722144,3722673,3722988,3722144,3722673,3722988,3722144,3722673,3722144,3722673,3722144,3722673,3722144,3722673,3722144,3722673,3722144,3722673,3722144,3722673,3722144,3722673,3722144,3722673,3722144,3722673,3722144,3722673,3722144,3722673,3722673,3722673,3722673</t>
+          <t>3722136,3722019,3722242,3722019,3722668,3722253,3722136,3722019,3722242,3722019,3722668,3722325,3722136,3722019,3722242,3722019,3722668,3722325,3722136,3722091,3722242,3722091,3722668,3722541,3722136,3722091,3722466,3722091,3722668,3722565,3722136,3722099,3722466,3722099,3722868,3722565,3722136,3722099,3722466,3722099,3722868,3722645,3722136,3722099,3722514,3722099,3722868,3722693,3722136,3722107,3722514,3722107,3722868,3722709,3722136,3722107,3722514,3722107,3722868,3723021,3722136,3722115,3722786,3722115,3722988,3723021,3722136,3722115,3722786,3722115,3722988,3722136,3722115,3722786,3722115,3722988,3722136,3722673,3722988,3722144,3722673,3722988,3722144,3722673,3722988,3722144,3722673,3722144,3722673,3722144,3722673,3722144,3722673,3722144,3722673,3722144,3722673,3722144,3722673,3722144,3722673,3722144,3722673,3722144,3722673,3722144,3722673,3722144,3722673,3722673,3722673,3722673</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L16 W12/25; N=112; EHP=3634.000000; air:2x3,air:11x2,air:12x3,air:13x2,air:14x3,normal:17x14,normal:18x14,fast:30x4,heavy:31x1,heavy:40x2,fast:58x3,fast:64x3,heavy:67x1,heavy:70x2,heavy:80x1,medium:83x5,swarm:84x31,heavy:86x1,heavy:88x1,fast:98x3,medium:108x5,medium:123x6,heavy:127x2</t>
+          <t>L16 W12/25; N=112; EHP=8988.973037; air:2x6,air:11x4,air:12x6,air:13x4,air:14x6,fast:30x4,fast:58x3,fast:64x3,fast:98x3,heavy:31x1,heavy:40x2,heavy:67x1,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x5,medium:108x5,medium:123x6,normal:17x14,normal:18x14,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>3724136,3724673,3724242,3724019,3724668,3724253,3724136,3724673,3724242,3724019,3724668,3724325,3724136,3724673,3724242,3724019,3724668,3724541,3724136,3724673,3724466,3724091,3724668,3724541,3724136,3724673,3724466,3724091,3724668,3724565,3724136,3724673,3724466,3724091,3724668,3724565,3724136,3724673,3724466,3724099,3724868,3724645,3724136,3724673,3724514,3724099,3724868,3724693,3724136,3724673,3724514,3724099,3724868,3724709,3724136,3724673,3724514,3724107,3724868,3725021,3724136,3724673,3724786,3724107,3724868,3725021,3724136,3724673,3724786,3724107,3724868,3724136,3724673,3724786,3724115,3724988,3724136,3724673,3724786,3724115,3724988,3724136,3724673,3724988,3724144,3724673,3724988,3724144,3724673,3724988,3724144,3724673,3724144,3724673,3724144,3724673,3724144,3724673,3724144,3724673,3724144,3724673,3724144,3724673,3724144,3724673,3724144,3724673,3724144,3724673,3724144,3724673,3724144,3724673,3724673,3724673,3724673,3724673</t>
+          <t>3724136,3724019,3724242,3724019,3724668,3724253,3724136,3724019,3724242,3724019,3724668,3724325,3724136,3724019,3724242,3724019,3724668,3724541,3724136,3724091,3724466,3724091,3724668,3724541,3724136,3724091,3724466,3724091,3724668,3724565,3724136,3724091,3724466,3724091,3724668,3724565,3724136,3724099,3724466,3724099,3724868,3724645,3724136,3724099,3724514,3724099,3724868,3724693,3724136,3724099,3724514,3724099,3724868,3724709,3724136,3724107,3724514,3724107,3724868,3725021,3724136,3724107,3724786,3724107,3724868,3725021,3724136,3724107,3724786,3724107,3724868,3724136,3724115,3724786,3724115,3724988,3724136,3724115,3724786,3724115,3724988,3724136,3724673,3724988,3724144,3724673,3724988,3724144,3724673,3724988,3724144,3724673,3724144,3724673,3724144,3724673,3724144,3724673,3724144,3724673,3724144,3724673,3724144,3724673,3724144,3724673,3724144,3724673,3724144,3724673,3724144,3724673,3724144,3724673,3724673,3724673,3724673,3724673</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L16 W13/25; N=118; EHP=4433.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x2,normal:17x15,normal:18x14,fast:30x3,heavy:31x1,heavy:40x1,fast:58x4,fast:64x3,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x33,heavy:86x1,heavy:88x1,fast:98x4,medium:108x6,medium:123x5,heavy:127x2</t>
+          <t>L16 W13/25; N=118; EHP=10968.996791; air:2x6,air:11x6,air:12x6,air:13x6,air:14x4,fast:30x3,fast:58x4,fast:64x3,fast:98x4,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x6,medium:108x6,medium:123x5,normal:17x15,normal:18x14,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>3726136,3726673,3726242,3726019,3726668,3726253,3726136,3726673,3726242,3726019,3726668,3726325,3726136,3726673,3726242,3726019,3726668,3726541,3726136,3726673,3726466,3726091,3726668,3726541,3726136,3726673,3726466,3726091,3726668,3726565,3726136,3726673,3726466,3726091,3726668,3726565,3726136,3726673,3726466,3726099,3726868,3726645,3726136,3726673,3726514,3726099,3726868,3726645,3726136,3726673,3726514,3726099,3726868,3726693,3726136,3726673,3726514,3726107,3726868,3726709,3726136,3726673,3726514,3726107,3726868,3726709,3726136,3726673,3726786,3726107,3726868,3727021,3726136,3726673,3726786,3726115,3726988,3726136,3726673,3726786,3726115,3726988,3726136,3726673,3726115,3726988,3726144,3726673,3726988,3726144,3726673,3726988,3726144,3726673,3726988,3726144,3726673,3726144,3726673,3726144,3726673,3726144,3726673,3726144,3726673,3726144,3726673,3726144,3726673,3726144,3726673,3726144,3726673,3726144,3726673,3726144,3726673,3726144,3726673,3726144,3726673,3726673,3726673,3726673</t>
+          <t>3726136,3726019,3726242,3726019,3726668,3726253,3726136,3726019,3726242,3726019,3726668,3726325,3726136,3726019,3726242,3726019,3726668,3726541,3726136,3726091,3726466,3726091,3726668,3726541,3726136,3726091,3726466,3726091,3726668,3726565,3726136,3726091,3726466,3726091,3726668,3726565,3726136,3726099,3726466,3726099,3726868,3726645,3726136,3726099,3726514,3726099,3726868,3726645,3726136,3726099,3726514,3726099,3726868,3726693,3726136,3726107,3726514,3726107,3726868,3726709,3726136,3726107,3726514,3726107,3726868,3726709,3726136,3726107,3726786,3726107,3726868,3727021,3726136,3726115,3726786,3726115,3726988,3726136,3726115,3726786,3726115,3726988,3726136,3726115,3726115,3726988,3726144,3726673,3726988,3726144,3726673,3726988,3726144,3726673,3726988,3726144,3726673,3726144,3726673,3726144,3726673,3726144,3726673,3726144,3726673,3726144,3726673,3726144,3726673,3726144,3726673,3726144,3726673,3726144,3726673,3726144,3726673,3726144,3726673,3726144,3726673,3726673,3726673,3726673</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L16 W14/25; N=124; EHP=5348.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x16,fast:30x3,heavy:31x1,heavy:40x1,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x6,swarm:84x34,heavy:86x1,heavy:88x2,fast:98x3,medium:108x6,medium:123x6,heavy:127x1</t>
+          <t>L16 W14/25; N=124; EHP=13235.051168; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x3,fast:58x4,fast:64x4,fast:98x3,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x1,heavy:88x2,heavy:127x1,medium:83x6,medium:108x6,medium:123x6,normal:17x15,normal:18x16,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>3728136,3728673,3728242,3728019,3728668,3728253,3728542,3728136,3728673,3728242,3728019,3728668,3728253,3728136,3728673,3728242,3728019,3728668,3728325,3728136,3728673,3728242,3728091,3728668,3728541,3728136,3728673,3728466,3728091,3728668,3728541,3728136,3728673,3728466,3728091,3728668,3728565,3728136,3728673,3728466,3728099,3728868,3728645,3728136,3728673,3728514,3728099,3728868,3728645,3728136,3728673,3728514,3728099,3728868,3728693,3728136,3728673,3728514,3728107,3728868,3728693,3728136,3728673,3728514,3728107,3728868,3728709,3728136,3728673,3728786,3728107,3728868,3728709,3728136,3728673,3728786,3728107,3728988,3729021,3728136,3728673,3728786,3728115,3728988,3728136,3728673,3728786,3728115,3728988,3728144,3728673,3728115,3728988,3728144,3728673,3728988,3728144,3728673,3728988,3728144,3728673,3728988,3728144,3728673,3728144,3728673,3728144,3728673,3728144,3728673,3728144,3728673,3728144,3728673,3728144,3728673,3728144,3728673,3728144,3728673,3728144,3728673,3728144,3728673,3728673,3728673,3728673,3728673,3728673,3728673</t>
+          <t>3728136,3728019,3728242,3728019,3728668,3728253,3728542,3728136,3728019,3728242,3728019,3728668,3728253,3728136,3728019,3728242,3728019,3728668,3728325,3728136,3728091,3728242,3728091,3728668,3728541,3728136,3728091,3728466,3728091,3728668,3728541,3728136,3728091,3728466,3728091,3728668,3728565,3728136,3728099,3728466,3728099,3728868,3728645,3728136,3728099,3728514,3728099,3728868,3728645,3728136,3728099,3728514,3728099,3728868,3728693,3728136,3728107,3728514,3728107,3728868,3728693,3728136,3728107,3728514,3728107,3728868,3728709,3728136,3728107,3728786,3728107,3728868,3728709,3728136,3728107,3728786,3728107,3728988,3729021,3728136,3728115,3728786,3728115,3728988,3728136,3728115,3728786,3728115,3728988,3728144,3728115,3728115,3728988,3728144,3728673,3728988,3728144,3728673,3728988,3728144,3728673,3728988,3728144,3728673,3728144,3728673,3728144,3728673,3728144,3728673,3728144,3728673,3728144,3728673,3728144,3728673,3728144,3728673,3728144,3728673,3728144,3728673,3728144,3728673,3728673,3728673,3728673,3728673,3728673,3728673</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L16 W15/25; N=130; EHP=9335.000000; air:2x3,air:11x3,air:12x3,air:13x4,air:14x3,normal:17x15,normal:18x15,fast:30x4,heavy:31x2,heavy:40x1,fast:58x3,fast:64x4,elite:67x1,heavy:67x2,heavy:70x1,heavy:80x2,medium:83x6,swarm:84x36,heavy:86x2,heavy:88x2,fast:98x4,medium:108x6,medium:123x7,heavy:127x1</t>
+          <t>L16 W15/25; N=130; EHP=23098.660590; air:2x6,air:11x6,air:12x6,air:13x8,air:14x6,elite:67x1,fast:30x4,fast:58x3,fast:64x4,fast:98x4,heavy:31x2,heavy:40x1,heavy:67x2,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x6,medium:108x6,medium:123x7,normal:17x15,normal:18x15,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>3730136,3730673,3730242,3730019,3730668,3730253,3730136,3730673,3730242,3730019,3730668,3730253,3730136,3730673,3730242,3730019,3730668,3730325,3730136,3730673,3730242,3730091,3730668,3730325,3730136,3730673,3730466,3730091,3730668,3730541,3730136,3730673,3730466,3730091,3730668,3730565,3730136,3730673,3730466,3730091,3730668,3730645,3730136,3730673,3730466,3730099,3730868,3730645,3730136,3730673,3730514,3730099,3730868,3730693,3730136,3730673,3730514,3730099,3730868,3730693,3730136,3730673,3730514,3730107,3730868,3730709,3730136,3730673,3730514,3730107,3730868,3730709,3730136,3730673,3730786,3730107,3730868,3731021,3730136,3730673,3730786,3730115,3730868,3730136,3730673,3730786,3730115,3730988,3730136,3730673,3730786,3730115,3730988,3730144,3730673,3730988,3730144,3730673,3730988,3730144,3730673,3730988,3730144,3730673,3730988,3730144,3730673,3730144,3730673,3730144,3730673,3730144,3730673,3730144,3730673,3730144,3730673,3730144,3730673,3730144,3730673,3730144,3730673,3730144,3730673,3730144,3730673,3730144,3730673,3730144,3730673,3730673,3730673,3730673,3730673,3730673</t>
+          <t>3730136,3730019,3730242,3730019,3730668,3730253,3730136,3730019,3730242,3730019,3730668,3730253,3730136,3730019,3730242,3730019,3730668,3730325,3730136,3730091,3730242,3730091,3730668,3730325,3730136,3730091,3730466,3730091,3730668,3730541,3730136,3730091,3730466,3730091,3730668,3730565,3730136,3730091,3730466,3730091,3730668,3730645,3730136,3730099,3730466,3730099,3730868,3730645,3730136,3730099,3730514,3730099,3730868,3730693,3730136,3730099,3730514,3730099,3730868,3730693,3730136,3730107,3730514,3730107,3730868,3730709,3730136,3730107,3730514,3730107,3730868,3730709,3730136,3730107,3730786,3730107,3730868,3731021,3730136,3730115,3730786,3730115,3730868,3730136,3730115,3730786,3730115,3730988,3730136,3730115,3730786,3730115,3730988,3730144,3730673,3730988,3730144,3730673,3730988,3730144,3730673,3730988,3730144,3730673,3730988,3730144,3730673,3730144,3730673,3730144,3730673,3730144,3730673,3730144,3730673,3730144,3730673,3730144,3730673,3730144,3730673,3730144,3730673,3730144,3730673,3730144,3730673,3730144,3730673,3730144,3730673,3730673,3730673,3730673,3730673,3730673</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L16 W16/25; N=136; EHP=9522.000000; air:2x3,air:11x4,air:12x3,air:13x3,air:14x3,normal:17x16,normal:18x17,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x7,swarm:84x38,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x6,heavy:127x1</t>
+          <t>L16 W16/25; N=136; EHP=23557.482020; air:2x6,air:11x8,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x7,medium:108x7,medium:123x6,normal:17x16,normal:18x17,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>3732136,3732673,3732242,3732019,3732668,3732253,3732136,3732673,3732242,3732019,3732668,3732253,3732136,3732673,3732242,3732019,3732668,3732325,3732136,3732673,3732242,3732091,3732668,3732325,3732136,3732673,3732466,3732091,3732668,3732541,3732136,3732673,3732466,3732091,3732668,3732565,3732136,3732673,3732466,3732099,3732668,3732565,3732136,3732673,3732466,3732099,3732868,3732645,3732136,3732673,3732514,3732099,3732868,3732645,3732136,3732673,3732514,3732099,3732868,3732693,3732136,3732673,3732514,3732107,3732868,3732693,3732136,3732673,3732514,3732107,3732868,3732709,3732136,3732673,3732786,3732107,3732868,3733021,3732136,3732673,3732786,3732115,3732868,3733021,3732136,3732673,3732786,3732115,3732988,3732136,3732673,3732786,3732115,3732988,3732136,3732673,3732786,3732115,3732988,3732144,3732673,3732988,3732144,3732673,3732988,3732144,3732673,3732988,3732144,3732673,3732988,3732144,3732673,3732144,3732673,3732144,3732673,3732144,3732673,3732144,3732673,3732144,3732673,3732144,3732673,3732144,3732673,3732144,3732673,3732144,3732673,3732144,3732673,3732144,3732673,3732144,3732673,3732673,3732673,3732673,3732673,3732673</t>
+          <t>3732136,3732019,3732242,3732019,3732668,3732253,3732136,3732019,3732242,3732019,3732668,3732253,3732136,3732019,3732242,3732019,3732668,3732325,3732136,3732091,3732242,3732091,3732668,3732325,3732136,3732091,3732466,3732091,3732668,3732541,3732136,3732091,3732466,3732091,3732668,3732565,3732136,3732099,3732466,3732099,3732668,3732565,3732136,3732099,3732466,3732099,3732868,3732645,3732136,3732099,3732514,3732099,3732868,3732645,3732136,3732099,3732514,3732099,3732868,3732693,3732136,3732107,3732514,3732107,3732868,3732693,3732136,3732107,3732514,3732107,3732868,3732709,3732136,3732107,3732786,3732107,3732868,3733021,3732136,3732115,3732786,3732115,3732868,3733021,3732136,3732115,3732786,3732115,3732988,3732136,3732115,3732786,3732115,3732988,3732136,3732115,3732786,3732115,3732988,3732144,3732673,3732988,3732144,3732673,3732988,3732144,3732673,3732988,3732144,3732673,3732988,3732144,3732673,3732144,3732673,3732144,3732673,3732144,3732673,3732144,3732673,3732144,3732673,3732144,3732673,3732144,3732673,3732144,3732673,3732144,3732673,3732144,3732673,3732144,3732673,3732144,3732673,3732673,3732673,3732673,3732673,3732673</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L16 W17/25; N=142; EHP=9713.000000; air:2x3,air:11x3,air:12x4,air:13x3,air:14x4,normal:17x17,normal:18x17,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x1,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x39,heavy:86x2,heavy:88x1,fast:98x5,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L16 W17/25; N=142; EHP=24033.602405; air:2x6,air:11x6,air:12x8,air:13x6,air:14x8,fast:30x4,fast:58x4,fast:64x4,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x7,medium:108x7,medium:123x7,normal:17x17,normal:18x17,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>3734136,3734673,3734242,3734019,3734668,3734253,3734136,3734673,3734242,3734019,3734668,3734253,3734136,3734673,3734242,3734019,3734668,3734325,3734136,3734673,3734242,3734019,3734668,3734325,3734136,3734673,3734466,3734091,3734668,3734541,3734136,3734673,3734466,3734091,3734668,3734541,3734136,3734673,3734466,3734091,3734668,3734565,3734136,3734673,3734466,3734099,3734868,3734565,3734136,3734673,3734466,3734099,3734868,3734645,3734136,3734673,3734514,3734099,3734868,3734693,3734136,3734673,3734514,3734099,3734868,3734693,3734136,3734673,3734514,3734107,3734868,3734709,3734136,3734673,3734514,3734107,3734868,3735021,3734136,3734673,3734786,3734107,3734868,3735021,3734136,3734673,3734786,3734107,3734988,3734136,3734673,3734786,3734115,3734988,3734136,3734673,3734786,3734115,3734988,3734136,3734673,3734115,3734988,3734144,3734673,3734988,3734144,3734673,3734988,3734144,3734673,3734988,3734144,3734673,3734988,3734144,3734673,3734144,3734673,3734144,3734673,3734144,3734673,3734144,3734673,3734144,3734673,3734144,3734673,3734144,3734673,3734144,3734673,3734144,3734673,3734144,3734673,3734144,3734673,3734144,3734673,3734144,3734673,3734673,3734673,3734673,3734673,3734673</t>
+          <t>3734136,3734019,3734242,3734019,3734668,3734253,3734136,3734019,3734242,3734019,3734668,3734253,3734136,3734019,3734242,3734019,3734668,3734325,3734136,3734019,3734242,3734019,3734668,3734325,3734136,3734091,3734466,3734091,3734668,3734541,3734136,3734091,3734466,3734091,3734668,3734541,3734136,3734091,3734466,3734091,3734668,3734565,3734136,3734099,3734466,3734099,3734868,3734565,3734136,3734099,3734466,3734099,3734868,3734645,3734136,3734099,3734514,3734099,3734868,3734693,3734136,3734099,3734514,3734099,3734868,3734693,3734136,3734107,3734514,3734107,3734868,3734709,3734136,3734107,3734514,3734107,3734868,3735021,3734136,3734107,3734786,3734107,3734868,3735021,3734136,3734107,3734786,3734107,3734988,3734136,3734115,3734786,3734115,3734988,3734136,3734115,3734786,3734115,3734988,3734136,3734115,3734115,3734988,3734144,3734673,3734988,3734144,3734673,3734988,3734144,3734673,3734988,3734144,3734673,3734988,3734144,3734673,3734144,3734673,3734144,3734673,3734144,3734673,3734144,3734673,3734144,3734673,3734144,3734673,3734144,3734673,3734144,3734673,3734144,3734673,3734144,3734673,3734144,3734673,3734144,3734673,3734144,3734673,3734673,3734673,3734673,3734673,3734673</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L16 W18/25; N=148; EHP=10378.000000; air:2x4,air:11x3,air:12x4,air:13x4,air:14x3,normal:17x18,normal:18x18,fast:30x4,heavy:31x2,heavy:40x2,fast:58x5,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x7,swarm:84x41,heavy:86x2,heavy:88x1,fast:98x4,medium:108x7,medium:123x8,heavy:127x2</t>
+          <t>L16 W18/25; N=148; EHP=25685.247535; air:2x8,air:11x6,air:12x8,air:13x8,air:14x6,fast:30x4,fast:58x5,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x7,medium:108x7,medium:123x8,normal:17x18,normal:18x18,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>3736136,3736673,3736242,3736019,3736668,3736253,3736136,3736673,3736242,3736019,3736668,3736253,3736136,3736673,3736242,3736019,3736668,3736325,3736136,3736673,3736242,3736019,3736668,3736325,3736136,3736673,3736242,3736091,3736668,3736541,3736136,3736673,3736466,3736091,3736668,3736541,3736136,3736673,3736466,3736091,3736668,3736565,3736136,3736673,3736466,3736091,3736668,3736565,3736136,3736673,3736466,3736099,3736868,3736645,3736136,3736673,3736514,3736099,3736868,3736645,3736136,3736673,3736514,3736099,3736868,3736693,3736136,3736673,3736514,3736107,3736868,3736709,3736136,3736673,3736514,3736107,3736868,3736709,3736136,3736673,3736514,3736107,3736868,3737021,3736136,3736673,3736786,3736107,3736868,3737021,3736136,3736673,3736786,3736115,3736868,3736136,3736673,3736786,3736115,3736988,3736136,3736673,3736786,3736115,3736988,3736136,3736673,3736988,3736144,3736673,3736988,3736144,3736673,3736988,3736144,3736673,3736988,3736144,3736673,3736988,3736144,3736673,3736144,3736673,3736144,3736673,3736144,3736673,3736144,3736673,3736144,3736673,3736144,3736673,3736144,3736673,3736144,3736673,3736144,3736673,3736144,3736673,3736144,3736673,3736144,3736673,3736144,3736673,3736673,3736673,3736673,3736673,3736673,3736673</t>
+          <t>3736136,3736019,3736242,3736019,3736668,3736253,3736136,3736019,3736242,3736019,3736668,3736253,3736136,3736019,3736242,3736019,3736668,3736325,3736136,3736019,3736242,3736019,3736668,3736325,3736136,3736091,3736242,3736091,3736668,3736541,3736136,3736091,3736466,3736091,3736668,3736541,3736136,3736091,3736466,3736091,3736668,3736565,3736136,3736091,3736466,3736091,3736668,3736565,3736136,3736099,3736466,3736099,3736868,3736645,3736136,3736099,3736514,3736099,3736868,3736645,3736136,3736099,3736514,3736099,3736868,3736693,3736136,3736107,3736514,3736107,3736868,3736709,3736136,3736107,3736514,3736107,3736868,3736709,3736136,3736107,3736514,3736107,3736868,3737021,3736136,3736107,3736786,3736107,3736868,3737021,3736136,3736115,3736786,3736115,3736868,3736136,3736115,3736786,3736115,3736988,3736136,3736115,3736786,3736115,3736988,3736136,3736673,3736988,3736144,3736673,3736988,3736144,3736673,3736988,3736144,3736673,3736988,3736144,3736673,3736988,3736144,3736673,3736144,3736673,3736144,3736673,3736144,3736673,3736144,3736673,3736144,3736673,3736144,3736673,3736144,3736673,3736144,3736673,3736144,3736673,3736144,3736673,3736144,3736673,3736144,3736673,3736144,3736673,3736673,3736673,3736673,3736673,3736673,3736673</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L16 W19/25; N=154; EHP=12020.000000; air:2x4,air:11x4,air:12x3,air:13x4,air:14x3,normal:17x19,normal:18x18,fast:30x5,heavy:31x2,heavy:40x2,fast:58x4,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x43,heavy:86x1,heavy:88x2,fast:98x4,medium:108x8,medium:123x7,heavy:127x2</t>
+          <t>L16 W19/25; N=154; EHP=29733.989486; air:2x8,air:11x8,air:12x6,air:13x8,air:14x6,fast:30x5,fast:58x4,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x7,normal:17x19,normal:18x18,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>3738136,3738673,3738242,3738019,3738668,3738253,3738542,3738136,3738673,3738242,3738019,3738668,3738253,3738136,3738673,3738242,3738019,3738668,3738325,3738136,3738673,3738242,3738091,3738668,3738325,3738136,3738673,3738242,3738091,3738668,3738541,3738136,3738673,3738466,3738091,3738668,3738541,3738136,3738673,3738466,3738091,3738668,3738565,3738136,3738673,3738466,3738099,3738668,3738565,3738136,3738673,3738466,3738099,3738868,3738645,3738136,3738673,3738466,3738099,3738868,3738645,3738136,3738673,3738514,3738099,3738868,3738693,3738136,3738673,3738514,3738107,3738868,3738693,3738136,3738673,3738514,3738107,3738868,3738709,3738136,3738673,3738514,3738107,3738868,3738709,3738136,3738673,3738786,3738107,3738868,3739021,3738136,3738673,3738786,3738115,3738868,3739021,3738136,3738673,3738786,3738115,3738988,3738136,3738673,3738786,3738115,3738988,3738144,3738673,3738786,3738115,3738988,3738144,3738673,3738988,3738144,3738673,3738988,3738144,3738673,3738988,3738144,3738673,3738988,3738144,3738673,3738988,3738144,3738673,3738144,3738673,3738144,3738673,3738144,3738673,3738144,3738673,3738144,3738673,3738144,3738673,3738144,3738673,3738144,3738673,3738144,3738673,3738144,3738673,3738144,3738673,3738144,3738673,3738673,3738673,3738673,3738673,3738673,3738673,3738673</t>
+          <t>3738136,3738019,3738242,3738019,3738668,3738253,3738542,3738136,3738019,3738242,3738019,3738668,3738253,3738136,3738019,3738242,3738019,3738668,3738325,3738136,3738091,3738242,3738091,3738668,3738325,3738136,3738091,3738242,3738091,3738668,3738541,3738136,3738091,3738466,3738091,3738668,3738541,3738136,3738091,3738466,3738091,3738668,3738565,3738136,3738099,3738466,3738099,3738668,3738565,3738136,3738099,3738466,3738099,3738868,3738645,3738136,3738099,3738466,3738099,3738868,3738645,3738136,3738099,3738514,3738099,3738868,3738693,3738136,3738107,3738514,3738107,3738868,3738693,3738136,3738107,3738514,3738107,3738868,3738709,3738136,3738107,3738514,3738107,3738868,3738709,3738136,3738107,3738786,3738107,3738868,3739021,3738136,3738115,3738786,3738115,3738868,3739021,3738136,3738115,3738786,3738115,3738988,3738136,3738115,3738786,3738115,3738988,3738144,3738115,3738786,3738115,3738988,3738144,3738673,3738988,3738144,3738673,3738988,3738144,3738673,3738988,3738144,3738673,3738988,3738144,3738673,3738988,3738144,3738673,3738144,3738673,3738144,3738673,3738144,3738673,3738144,3738673,3738144,3738673,3738144,3738673,3738144,3738673,3738144,3738673,3738144,3738673,3738144,3738673,3738144,3738673,3738144,3738673,3738673,3738673,3738673,3738673,3738673,3738673,3738673</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L16 W20/25; N=160; EHP=20181.000000; air:2x3,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x18,normal:18x19,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x4,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x44,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L16 W20/25; N=160; EHP=49916.313979; air:2x6,air:11x8,air:12x8,air:13x8,air:14x8,elite:67x1,fast:30x5,fast:58x5,fast:64x4,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x18,normal:18x19,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10018009,10018019,10018011,10048620,10018018,10018012,10018009,10018019,10018011,10048620,10018018,10018012,10018009,10018019,10018011,10048620,10018018,10045190,10018009,10018019,10018011,10048620,10018018,10045190,10018009,10018019,10018013,10018006,10018018,10018015,10018009,10018019,10018013,10018006,10018018,10018015,10018009,10018019,10018013,10018006,10018018,10018016,10018009,10018019,10018013,10018006,10018018,10018016,10018009,10018019,10018013,10048621,10018023,10018017,10018009,10018019,10018014,10048621,10018023,10018017,10018009,10018019,10018014,10048621,10018023,10018020,10018009,10018019,10018014,10048621,10018023,10018020,10018009,10018019,10018014,10018007,10018023,10018021,10018009,10018019,10018014,10018007,10018023,10018021,10018009,10018019,10018022,10018007,10018023,10018025,10018009,10018019,10018022,10018007,10018023,10018025,10018009,10018019,10018022,10018008,10018024,10018009,10018019,10018022,10018008,10018024,10018009,10018019,10018022,10018008,10018024,10018009,10018019,10018008,10018024,10018009,10018019,10018024,10018010,10018019,10018024,10018010,10018019,10018024,10018010,10018019,10018024,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018019,10018019,10018019,10018019,10018019</t>
+          <t>10018009,10048620,10018011,10048620,10018018,10018012,10018009,10048620,10018011,10048620,10018018,10018012,10018009,10048620,10018011,10048620,10018018,10045190,10018009,10048620,10018011,10048620,10018018,10045190,10018009,10018006,10018013,10018006,10018018,10018015,10018009,10018006,10018013,10018006,10018018,10018015,10018009,10018006,10018013,10018006,10018018,10018016,10018009,10018006,10018013,10018006,10018018,10018016,10018009,10048621,10018013,10048621,10018023,10018017,10018009,10048621,10018014,10048621,10018023,10018017,10018009,10048621,10018014,10048621,10018023,10018020,10018009,10048621,10018014,10048621,10018023,10018020,10018009,10018007,10018014,10018007,10018023,10018021,10018009,10018007,10018014,10018007,10018023,10018021,10018009,10018007,10018022,10018007,10018023,10018025,10018009,10018007,10018022,10018007,10018023,10018025,10018009,10018008,10018022,10018008,10018024,10018009,10018008,10018022,10018008,10018024,10018009,10018008,10018022,10018008,10018024,10018009,10018008,10018008,10018024,10018009,10018019,10018024,10018010,10018019,10018024,10018010,10018019,10018024,10018010,10018019,10018024,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018010,10018019,10018019,10018019,10018019,10018019,10018019</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L16 W21/25; N=166; EHP=20585.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x21,normal:18x20,fast:30x4,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x46,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L16 W21/25; N=166; EHP=50941.760983; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x4,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x21,normal:18x20,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10018029,10018040,10018031,10048622,10018039,10018032,10018029,10018040,10018031,10048622,10018039,10018032,10018029,10018040,10018031,10048622,10018039,10018033,10018029,10018040,10018031,10048622,10018039,10018033,10018029,10018040,10018031,10018026,10018039,10018036,10018029,10018040,10018034,10018026,10018039,10018036,10018029,10018040,10018034,10018026,10018039,10018037,10018029,10018040,10018034,10018026,10018039,10018037,10018029,10018040,10018034,10048623,10018044,10018037,10018029,10018040,10018034,10048623,10018044,10018038,10018029,10018040,10018035,10048623,10018044,10018038,10018029,10018040,10018035,10048623,10018044,10018041,10018029,10018040,10018035,10018027,10018044,10018041,10018029,10018040,10018035,10018027,10018044,10018042,10018029,10018040,10018035,10018027,10018044,10018042,10018029,10018040,10018043,10018027,10018044,10045191,10018029,10018040,10018043,10018028,10018044,10045191,10018029,10018040,10018043,10018028,10018045,10018029,10018040,10018043,10018028,10018045,10018029,10018040,10018043,10018028,10018045,10018030,10018040,10018028,10018045,10018030,10018040,10018045,10018030,10018040,10018045,10018030,10018040,10018045,10018030,10018040,10018045,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018040,10018040,10018040,10018040,10018040,10018040,10018040</t>
+          <t>10018029,10048622,10018031,10048622,10018039,10018032,10018029,10048622,10018031,10048622,10018039,10018032,10018029,10048622,10018031,10048622,10018039,10018033,10018029,10048622,10018031,10048622,10018039,10018033,10018029,10018026,10018031,10018026,10018039,10018036,10018029,10018026,10018034,10018026,10018039,10018036,10018029,10018026,10018034,10018026,10018039,10018037,10018029,10018026,10018034,10018026,10018039,10018037,10018029,10048623,10018034,10048623,10018044,10018037,10018029,10048623,10018034,10048623,10018044,10018038,10018029,10048623,10018035,10048623,10018044,10018038,10018029,10048623,10018035,10048623,10018044,10018041,10018029,10018027,10018035,10018027,10018044,10018041,10018029,10018027,10018035,10018027,10018044,10018042,10018029,10018027,10018035,10018027,10018044,10018042,10018029,10018027,10018043,10018027,10018044,10045191,10018029,10018028,10018043,10018028,10018044,10045191,10018029,10018028,10018043,10018028,10018045,10018029,10018028,10018043,10018028,10018045,10018029,10018028,10018043,10018028,10018045,10018030,10018028,10018028,10018045,10018030,10018040,10018045,10018030,10018040,10018045,10018030,10018040,10018045,10018030,10018040,10018045,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018030,10018040,10018040,10018040,10018040,10018040,10018040,10018040,10018040</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L16 W22/25; N=172; EHP=20997.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x5,normal:17x20,normal:18x21,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x3,heavy:80x2,medium:83x8,swarm:84x48,heavy:86x2,heavy:88x2,fast:98x5,medium:108x9,medium:123x8,heavy:127x2</t>
+          <t>L16 W22/25; N=172; EHP=51968.369538; air:2x8,air:11x8,air:12x8,air:13x8,air:14x10,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x9,medium:123x8,normal:17x20,normal:18x21,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10018049,10018059,10018051,10048624,10018058,10018052,10018049,10018059,10018051,10048624,10018058,10018052,10018049,10018059,10018051,10048624,10018058,10018053,10018049,10018059,10018051,10048624,10018058,10018053,10018049,10018059,10018051,10018046,10018058,10018056,10018049,10018059,10018054,10018046,10018058,10018056,10018049,10018059,10018054,10018046,10018058,10018056,10018049,10018059,10018054,10018046,10018058,10045192,10018049,10018059,10018054,10048625,10018058,10045192,10018049,10018059,10018054,10048625,10018063,10018057,10018049,10018059,10018055,10048625,10018063,10018057,10018049,10018059,10018055,10048625,10018063,10018060,10018049,10018059,10018055,10048625,10018063,10018060,10018049,10018059,10018055,10018047,10018063,10018061,10018049,10018059,10018055,10018047,10018063,10018061,10018049,10018059,10018055,10018047,10018063,10018065,10018049,10018059,10018062,10018047,10018063,10018065,10018049,10018059,10018062,10018048,10018064,10018049,10018059,10018062,10018048,10018064,10018049,10018059,10018062,10018048,10018064,10018049,10018059,10018062,10018048,10018064,10018049,10018059,10018064,10018050,10018059,10018064,10018050,10018059,10018064,10018050,10018059,10018064,10018050,10018059,10018064,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018059,10018059,10018059,10018059,10018059</t>
+          <t>10018049,10048624,10018051,10048624,10018058,10018052,10018049,10048624,10018051,10048624,10018058,10018052,10018049,10048624,10018051,10048624,10018058,10018053,10018049,10048624,10018051,10048624,10018058,10018053,10018049,10018046,10018051,10018046,10018058,10018056,10018049,10018046,10018054,10018046,10018058,10018056,10018049,10018046,10018054,10018046,10018058,10018056,10018049,10018046,10018054,10018046,10018058,10045192,10018049,10048625,10018054,10048625,10018058,10045192,10018049,10048625,10018054,10048625,10018063,10018057,10018049,10048625,10018055,10048625,10018063,10018057,10018049,10048625,10018055,10048625,10018063,10018060,10018049,10048625,10018055,10048625,10018063,10018060,10018049,10018047,10018055,10018047,10018063,10018061,10018049,10018047,10018055,10018047,10018063,10018061,10018049,10018047,10018055,10018047,10018063,10018065,10018049,10018047,10018062,10018047,10018063,10018065,10018049,10018048,10018062,10018048,10018064,10018049,10018048,10018062,10018048,10018064,10018049,10018048,10018062,10018048,10018064,10018049,10018048,10018062,10018048,10018064,10018049,10018059,10018064,10018050,10018059,10018064,10018050,10018059,10018064,10018050,10018059,10018064,10018050,10018059,10018064,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018050,10018059,10018059,10018059,10018059,10018059,10018059</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L16 W23/25; N=178; EHP=21417.000000; air:2x4,air:11x4,air:12x5,air:13x4,air:14x4,normal:17x22,normal:18x22,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x6,heavy:67x3,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x49,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x9,heavy:127x2</t>
+          <t>L16 W23/25; N=178; EHP=52987.206454; air:2x8,air:11x8,air:12x10,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x6,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x3,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x9,medium:108x8,medium:123x9,normal:17x22,normal:18x22,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10018069,10018079,10018071,10048626,10018078,10018072,10018069,10018079,10018071,10048626,10018078,10018072,10018069,10018079,10018071,10048626,10018078,10018073,10018069,10018079,10018071,10048626,10018078,10018073,10018069,10018079,10018071,10048626,10018078,10045193,10018069,10018079,10018071,10018066,10018078,10045193,10018069,10018079,10018074,10018066,10018078,10018076,10018069,10018079,10018074,10018066,10018078,10018076,10018069,10018079,10018074,10018066,10018078,10018077,10018069,10018079,10018074,10048627,10018083,10018077,10018069,10018079,10018074,10048627,10018083,10018077,10018069,10018079,10018075,10048627,10018083,10018080,10018069,10018079,10018075,10048627,10018083,10018080,10018069,10018079,10018075,10018067,10018083,10018081,10018069,10018079,10018075,10018067,10018083,10018081,10018069,10018079,10018075,10018067,10018083,10018081,10018069,10018079,10018082,10018067,10018083,10018085,10018069,10018079,10018082,10018067,10018083,10018085,10018069,10018079,10018082,10018068,10018084,10018069,10018079,10018082,10018068,10018084,10018069,10018079,10018082,10018068,10018084,10018069,10018079,10018082,10018068,10018084,10018070,10018079,10018084,10018070,10018079,10018084,10018070,10018079,10018084,10018070,10018079,10018084,10018070,10018079,10018084,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018079,10018079,10018079,10018079,10018079,10018079,10018079</t>
+          <t>10018069,10048626,10018071,10048626,10018078,10018072,10018069,10048626,10018071,10048626,10018078,10018072,10018069,10048626,10018071,10048626,10018078,10018073,10018069,10048626,10018071,10048626,10018078,10018073,10018069,10048626,10018071,10048626,10018078,10045193,10018069,10018066,10018071,10018066,10018078,10045193,10018069,10018066,10018074,10018066,10018078,10018076,10018069,10018066,10018074,10018066,10018078,10018076,10018069,10018066,10018074,10018066,10018078,10018077,10018069,10048627,10018074,10048627,10018083,10018077,10018069,10048627,10018074,10048627,10018083,10018077,10018069,10048627,10018075,10048627,10018083,10018080,10018069,10048627,10018075,10048627,10018083,10018080,10018069,10018067,10018075,10018067,10018083,10018081,10018069,10018067,10018075,10018067,10018083,10018081,10018069,10018067,10018075,10018067,10018083,10018081,10018069,10018067,10018082,10018067,10018083,10018085,10018069,10018067,10018082,10018067,10018083,10018085,10018069,10018068,10018082,10018068,10018084,10018069,10018068,10018082,10018068,10018084,10018069,10018068,10018082,10018068,10018084,10018069,10018068,10018082,10018068,10018084,10018070,10018079,10018084,10018070,10018079,10018084,10018070,10018079,10018084,10018070,10018079,10018084,10018070,10018079,10018084,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018070,10018079,10018079,10018079,10018079,10018079,10018079,10018079,10018079</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L16 W24/25; N=184; EHP=22934.000000; air:2x5,air:11x4,air:12x4,air:13x5,air:14x4,normal:17x22,normal:18x22,fast:30x6,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x3,medium:83x9,swarm:84x51,heavy:86x2,heavy:88x3,fast:98x6,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L16 W24/25; N=184; EHP=56748.035301; air:2x10,air:11x8,air:12x8,air:13x10,air:14x8,fast:30x6,fast:58x5,fast:64x5,fast:98x6,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x3,heavy:86x2,heavy:88x3,heavy:127x2,medium:83x9,medium:108x9,medium:123x9,normal:17x22,normal:18x22,swarm:84x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10018089,10018100,10018091,10048628,10018099,10018092,10018107,10018089,10018100,10018091,10048628,10018099,10018092,10018089,10018100,10018091,10048628,10018099,10018092,10018089,10018100,10018091,10048628,10018099,10018093,10018089,10018100,10018091,10018086,10018099,10018093,10018089,10018100,10018094,10018086,10018099,10018096,10018089,10018100,10018094,10018086,10018099,10018096,10018089,10018100,10018094,10018086,10018099,10018097,10018089,10018100,10018094,10018086,10018099,10018097,10018089,10018100,10018094,10048629,10018104,10018098,10018089,10018100,10018094,10048629,10018104,10018098,10018089,10018100,10018095,10048629,10018104,10018098,10018089,10018100,10018095,10048629,10018104,10018101,10018089,10018100,10018095,10018087,10018104,10018101,10018089,10018100,10018095,10018087,10018104,10018101,10018089,10018100,10018095,10018087,10018104,10018102,10018089,10018100,10018103,10018087,10018104,10018102,10018089,10018100,10018103,10018087,10018104,10018106,10018089,10018100,10018103,10018088,10018104,10018106,10018089,10018100,10018103,10018088,10018105,10018089,10018100,10018103,10018088,10018105,10018089,10018100,10018103,10018088,10018105,10018090,10018100,10018088,10018105,10018090,10018100,10018105,10018090,10018100,10018105,10018090,10018100,10018105,10018090,10018100,10018105,10018090,10018100,10018105,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018100,10018100,10018100,10018100,10018100,10018100,10018100,10018100,10018100</t>
+          <t>10018089,10048628,10018091,10048628,10018099,10018092,10018107,10018089,10048628,10018091,10048628,10018099,10018092,10018089,10048628,10018091,10048628,10018099,10018092,10018089,10048628,10018091,10048628,10018099,10018093,10018089,10018086,10018091,10018086,10018099,10018093,10018089,10018086,10018094,10018086,10018099,10018096,10018089,10018086,10018094,10018086,10018099,10018096,10018089,10018086,10018094,10018086,10018099,10018097,10018089,10018086,10018094,10018086,10018099,10018097,10018089,10048629,10018094,10048629,10018104,10018098,10018089,10048629,10018094,10048629,10018104,10018098,10018089,10048629,10018095,10048629,10018104,10018098,10018089,10048629,10018095,10048629,10018104,10018101,10018089,10018087,10018095,10018087,10018104,10018101,10018089,10018087,10018095,10018087,10018104,10018101,10018089,10018087,10018095,10018087,10018104,10018102,10018089,10018087,10018103,10018087,10018104,10018102,10018089,10018087,10018103,10018087,10018104,10018106,10018089,10018088,10018103,10018088,10018104,10018106,10018089,10018088,10018103,10018088,10018105,10018089,10018088,10018103,10018088,10018105,10018089,10018088,10018103,10018088,10018105,10018090,10018088,10018088,10018105,10018090,10018100,10018105,10018090,10018100,10018105,10018090,10018100,10018105,10018090,10018100,10018105,10018090,10018100,10018105,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018090,10018100,10018100,10018100,10018100,10018100,10018100,10018100,10018100,10018100,10018100</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L16 W25/25; N=190; EHP=45775.000000; air:2x4,air:11x5,air:12x4,air:13x5,air:14x5,normal:17x22,normal:18x22,fast:30x5,heavy:31x3,heavy:40x2,fast:58x6,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x3,medium:83x9,swarm:84x53,heavy:86x3,heavy:88x2,fast:98x6,medium:108x10,medium:123x9,heavy:127x2,boss:132x1</t>
+          <t>L16 W25/25; N=190; EHP=113253.466418; air:2x8,air:11x10,air:12x8,air:13x10,air:14x10,boss:132x1,fast:30x5,fast:58x6,fast:64x5,fast:98x6,heavy:31x3,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x3,heavy:86x3,heavy:88x2,heavy:127x2,medium:83x9,medium:108x10,medium:123x9,normal:17x22,normal:18x22,swarm:84x30 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L16/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L16/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>250</v>
+        <v>340</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>243</v>
+        <v>310</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>236</v>
+        <v>270</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>229</v>
+        <v>350</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>222</v>
+        <v>290</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>208</v>
+        <v>280</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>201</v>
+        <v>260</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>194</v>
+        <v>350</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>187</v>
+        <v>270</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>180</v>
+        <v>290</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>166</v>
+        <v>290</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>159</v>
+        <v>270</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>152</v>
+        <v>240</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>145</v>
+        <v>350</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>138</v>
+        <v>270</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>131</v>
+        <v>290</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>128</v>
+        <v>250</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>270</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>350</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>210</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
